--- a/Design/Excel/ET/Datas/Product/CustomerFlowConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/CustomerFlowConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1477,6 +1477,408 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1,2,3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>1,2,3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1,2,3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Design/Excel/ET/Datas/Product/CustomerFlowConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/CustomerFlowConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1879,6 +1879,140 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>1,2,3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>1,2,3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Design/Excel/ET/Datas/Product/CustomerFlowConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/CustomerFlowConfig.xlsx
@@ -2700,16 +2700,16 @@
         <v>1101</v>
       </c>
       <c r="D32" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="E32" t="n">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="F32" t="n">
         <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>300</v>
+        <v>1200</v>
       </c>
       <c r="H32" t="n">
         <v>60</v>
@@ -2740,16 +2740,16 @@
         <v>1102</v>
       </c>
       <c r="D33" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="E33" t="n">
-        <v>100</v>
+        <v>440</v>
       </c>
       <c r="F33" t="n">
         <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="H33" t="n">
         <v>60</v>
@@ -2780,16 +2780,16 @@
         <v>1103</v>
       </c>
       <c r="D34" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="E34" t="n">
-        <v>80</v>
+        <v>360</v>
       </c>
       <c r="F34" t="n">
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>260</v>
+        <v>900</v>
       </c>
       <c r="H34" t="n">
         <v>60</v>
